--- a/exports/COLPAL_full_report.xlsx
+++ b/exports/COLPAL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>2.23</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1450</v>
+        <v>1418.75</v>
       </c>
       <c r="I2" t="n">
         <v>1429.45</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.82</v>
+        <v>-2.96</v>
       </c>
       <c r="L2" t="n">
-        <v>2.39</v>
+        <v>3.08</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>0.41</v>
       </c>
       <c r="N2" t="n">
-        <v>1.32</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
         <v>-0.4</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>5.19</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44595.38541666666</v>
+        <v>44595.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>1453.1</v>
+        <v>1469</v>
       </c>
       <c r="I3" t="n">
         <v>1462.086444978788</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.42</v>
+        <v>-3.54</v>
       </c>
       <c r="L3" t="n">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="M3" t="n">
         <v>0.57</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>4.61</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44615.55208333334</v>
+        <v>44616.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>1433.95</v>
+        <v>1405.2</v>
       </c>
       <c r="I4" t="n">
         <v>1406.772748140471</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.39</v>
+        <v>-4.34</v>
       </c>
       <c r="L4" t="n">
         <v>5.37</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>4.42</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1449.75</v>
+        <v>1489.2</v>
       </c>
       <c r="I5" t="n">
         <v>1453.839120793262</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.17</v>
+        <v>-5.98</v>
       </c>
       <c r="L5" t="n">
-        <v>3.54</v>
+        <v>6.68</v>
       </c>
       <c r="M5" t="n">
-        <v>0.68</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.98</v>
+        <v>3.12</v>
       </c>
       <c r="O5" t="n">
         <v>-2.93</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>6.02</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44663.38541666666</v>
+        <v>44663.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>1556.15</v>
+        <v>1532.5</v>
       </c>
       <c r="I6" t="n">
         <v>1536.005068964936</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>2.91</v>
       </c>
       <c r="L6" t="n">
         <v>1.99</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>4.54</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44672.55208333334</v>
+        <v>44673.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>1547</v>
+        <v>1609</v>
       </c>
       <c r="I7" t="n">
         <v>1588.170612450514</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.95</v>
+        <v>-4.99</v>
       </c>
       <c r="L7" t="n">
-        <v>2.71</v>
+        <v>4.99</v>
       </c>
       <c r="M7" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>1.91</v>
+        <v>3.49</v>
       </c>
       <c r="O7" t="n">
         <v>-1.89</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.32</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44686.38541666666</v>
+        <v>44686.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>1610.25</v>
+        <v>1569.45</v>
       </c>
       <c r="I8" t="n">
         <v>1588.985762717267</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08</v>
+        <v>-2.46</v>
       </c>
       <c r="L8" t="n">
         <v>3.73</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>6.3</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44747.55208333334</v>
+        <v>44748.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1529.35</v>
+        <v>1554.05</v>
       </c>
       <c r="I9" t="n">
         <v>1543.860510130078</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>61</v>
+        <v>61.83333333333334</v>
       </c>
       <c r="K9" t="n">
-        <v>2.56</v>
+        <v>0.98</v>
       </c>
       <c r="L9" t="n">
         <v>5.11</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.79</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44767.55208333334</v>
+        <v>44768.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1561</v>
+        <v>1546.05</v>
       </c>
       <c r="I10" t="n">
         <v>1551.510342704594</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>0.45</v>
+        <v>-0.51</v>
       </c>
       <c r="L10" t="n">
         <v>2.06</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>5.21</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44777.55208333334</v>
+        <v>44778.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1594</v>
+        <v>1609.95</v>
       </c>
       <c r="I11" t="n">
         <v>1605.388814862728</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.1</v>
+        <v>-4.13</v>
       </c>
       <c r="L11" t="n">
-        <v>4.12</v>
+        <v>4.46</v>
       </c>
       <c r="M11" t="n">
         <v>0.9</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>4.6</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1627.8</v>
+        <v>1589.35</v>
       </c>
       <c r="I12" t="n">
         <v>1606.425389975898</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K12" t="n">
-        <v>1.11</v>
+        <v>-1.28</v>
       </c>
       <c r="L12" t="n">
         <v>3.91</v>
@@ -1125,7 +1268,7 @@
         <v>1.19</v>
       </c>
       <c r="N12" t="n">
-        <v>1.63</v>
+        <v>3.24</v>
       </c>
       <c r="O12" t="n">
         <v>1.07</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>5.4</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44861.38541666666</v>
+        <v>44861.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>1605.15</v>
+        <v>1624.75</v>
       </c>
       <c r="I13" t="n">
         <v>1624.543874548538</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.99</v>
+        <v>-2.23</v>
       </c>
       <c r="L13" t="n">
         <v>3.12</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.7</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44881.38541666666</v>
+        <v>44881.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>1570.85</v>
+        <v>1564</v>
       </c>
       <c r="I14" t="n">
         <v>1570.840232894893</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.32</v>
+        <v>-3.74</v>
       </c>
       <c r="L14" t="n">
         <v>4.29</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>4.27</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44895.38541666666</v>
+        <v>44895.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>1619.95</v>
+        <v>1631.05</v>
       </c>
       <c r="I15" t="n">
         <v>1622.103199892179</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.58</v>
+        <v>-4.29</v>
       </c>
       <c r="L15" t="n">
-        <v>4.61</v>
+        <v>4.86</v>
       </c>
       <c r="M15" t="n">
         <v>0.39</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>3.62</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44908.55208333334</v>
+        <v>44909.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1639</v>
+        <v>1581.95</v>
       </c>
       <c r="I16" t="n">
         <v>1596.788613121519</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>0.49</v>
+        <v>-3.01</v>
       </c>
       <c r="L16" t="n">
-        <v>3.03</v>
+        <v>3.26</v>
       </c>
       <c r="M16" t="n">
         <v>0.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.48</v>
+        <v>3.97</v>
       </c>
       <c r="O16" t="n">
         <v>1.62</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.11</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44985.55208333334</v>
+        <v>44986.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1478</v>
+        <v>1484.3</v>
       </c>
       <c r="I17" t="n">
         <v>1483.892658089547</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>76.16666666666667</v>
+        <v>77</v>
       </c>
       <c r="K17" t="n">
-        <v>6.57</v>
+        <v>6.17</v>
       </c>
       <c r="L17" t="n">
         <v>3.67</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>3.27</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45068.55208333334</v>
+        <v>45069.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1611</v>
+        <v>1597.9</v>
       </c>
       <c r="I18" t="n">
         <v>1598.508219388141</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>82.16666666666667</v>
+        <v>83</v>
       </c>
       <c r="K18" t="n">
-        <v>8.539999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="L18" t="n">
         <v>0.8100000000000001</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>5.06</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45089.55208333334</v>
+        <v>45090.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1627.3</v>
+        <v>1650.85</v>
       </c>
       <c r="I19" t="n">
         <v>1644.561309502816</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.84</v>
+        <v>-3.31</v>
       </c>
       <c r="L19" t="n">
-        <v>2.76</v>
+        <v>4.39</v>
       </c>
       <c r="M19" t="n">
         <v>0.49</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.03</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45159.55208333334</v>
+        <v>45160.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1995</v>
+        <v>1928.4</v>
       </c>
       <c r="I20" t="n">
         <v>1931.774036594971</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>69.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K20" t="n">
-        <v>20.85</v>
+        <v>16.81</v>
       </c>
       <c r="L20" t="n">
         <v>1.56</v>
@@ -1581,7 +1820,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>1.8</v>
+        <v>2.43</v>
       </c>
       <c r="O20" t="n">
         <v>1.39</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>6.71</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45174.55208333334</v>
+        <v>45175.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1990</v>
+        <v>2020.05</v>
       </c>
       <c r="I21" t="n">
         <v>2012.601603473785</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.19</v>
+        <v>-4.75</v>
       </c>
       <c r="L21" t="n">
-        <v>4.36</v>
+        <v>5.35</v>
       </c>
       <c r="M21" t="n">
         <v>0.92</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>4.63</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45182.55208333334</v>
+        <v>45183.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1964.05</v>
+        <v>1939.35</v>
       </c>
       <c r="I22" t="n">
         <v>1949.930138422152</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.77</v>
+        <v>-3.99</v>
       </c>
       <c r="L22" t="n">
-        <v>3.27</v>
+        <v>4.43</v>
       </c>
       <c r="M22" t="n">
         <v>0.23</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>4.81</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45195.38541666666</v>
+        <v>45195.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>2003.8</v>
+        <v>2080.05</v>
       </c>
       <c r="I23" t="n">
         <v>2019.850988605402</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.32</v>
+        <v>-7.26</v>
       </c>
       <c r="L23" t="n">
-        <v>4.1</v>
+        <v>7.44</v>
       </c>
       <c r="M23" t="n">
         <v>0.66</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.88</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45300.55208333334</v>
+        <v>45301.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>2439.6</v>
+        <v>2404.9</v>
       </c>
       <c r="I24" t="n">
         <v>2423.566902273338</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>105</v>
+        <v>105.8333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>17.29</v>
+        <v>15.62</v>
       </c>
       <c r="L24" t="n">
         <v>5.38</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>4.75</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45307.38541666666</v>
+        <v>45307.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>2493.1</v>
+        <v>2500</v>
       </c>
       <c r="I25" t="n">
         <v>2496.954412438955</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.67</v>
+        <v>-3.95</v>
       </c>
       <c r="L25" t="n">
         <v>4.99</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.79</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45349.55208333334</v>
+        <v>45350.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>2532.8</v>
+        <v>2487.9</v>
       </c>
       <c r="I26" t="n">
         <v>2488.776593863762</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>42</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K26" t="n">
-        <v>1.31</v>
+        <v>-0.48</v>
       </c>
       <c r="L26" t="n">
         <v>4.84</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>5.35</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45362.38541666666</v>
+        <v>45362.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>2594.85</v>
+        <v>2603.1</v>
       </c>
       <c r="I27" t="n">
         <v>2599.877129839428</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.3</v>
+        <v>-4.63</v>
       </c>
       <c r="L27" t="n">
         <v>5.51</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.48</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45390.55208333334</v>
+        <v>45391.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>2698.05</v>
+        <v>2639</v>
       </c>
       <c r="I28" t="n">
         <v>2654.067825821267</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>3.65</v>
+        <v>1.38</v>
       </c>
       <c r="L28" t="n">
         <v>2.74</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>6.34</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45406.55208333334</v>
+        <v>45407.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>2751</v>
+        <v>2780.15</v>
       </c>
       <c r="I29" t="n">
         <v>2761.315557915704</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.24</v>
+        <v>-5.35</v>
       </c>
       <c r="L29" t="n">
-        <v>4.4</v>
+        <v>5.49</v>
       </c>
       <c r="M29" t="n">
         <v>0.47</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>5.1</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45426.55208333334</v>
+        <v>45427.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>2818</v>
+        <v>2704</v>
       </c>
       <c r="I30" t="n">
         <v>2730.739537322669</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K30" t="n">
-        <v>1.36</v>
+        <v>-2.74</v>
       </c>
       <c r="L30" t="n">
-        <v>1.54</v>
+        <v>3.28</v>
       </c>
       <c r="M30" t="n">
         <v>0.42</v>
       </c>
       <c r="N30" t="n">
-        <v>2.61</v>
+        <v>5.11</v>
       </c>
       <c r="O30" t="n">
         <v>1.4</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.52</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>2694</v>
+        <v>2772.95</v>
       </c>
       <c r="I31" t="n">
         <v>2766.655963359623</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>0.37</v>
+        <v>-2.55</v>
       </c>
       <c r="L31" t="n">
         <v>5.43</v>
@@ -2208,7 +2579,7 @@
         <v>2.12</v>
       </c>
       <c r="N31" t="n">
-        <v>1.85</v>
+        <v>4.27</v>
       </c>
       <c r="O31" t="n">
         <v>-5.11</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.91</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45576.55208333334</v>
+        <v>45579.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>3685</v>
+        <v>3563.8</v>
       </c>
       <c r="I32" t="n">
         <v>3637.817822033277</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>129.1666666666667</v>
+        <v>132</v>
       </c>
       <c r="K32" t="n">
-        <v>32.89</v>
+        <v>28.52</v>
       </c>
       <c r="L32" t="n">
         <v>3.69</v>
@@ -2265,7 +2648,7 @@
         <v>2.02</v>
       </c>
       <c r="N32" t="n">
-        <v>2.45</v>
+        <v>4.75</v>
       </c>
       <c r="O32" t="n">
         <v>4.27</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>180</v>
+        <v>181</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>7.41</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>2718</v>
+        <v>2835.45</v>
       </c>
       <c r="I33" t="n">
         <v>2815.36910507906</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K33" t="n">
-        <v>23.73</v>
+        <v>20.44</v>
       </c>
       <c r="L33" t="n">
         <v>3.82</v>
       </c>
       <c r="M33" t="n">
-        <v>0.87</v>
+        <v>1.56</v>
       </c>
       <c r="N33" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="O33" t="n">
         <v>-4.75</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.75</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45625.38541666666</v>
+        <v>45625.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>2924.85</v>
+        <v>2885</v>
       </c>
       <c r="I34" t="n">
         <v>2894.142792865353</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>3.15</v>
+        <v>1.75</v>
       </c>
       <c r="L34" t="n">
         <v>3.23</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.02</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45660.38541666666</v>
+        <v>45660.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>2795.5</v>
+        <v>2818.9</v>
       </c>
       <c r="I35" t="n">
         <v>2814.079764270352</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>34.83333333333334</v>
+        <v>35</v>
       </c>
       <c r="K35" t="n">
-        <v>3.1</v>
+        <v>2.29</v>
       </c>
       <c r="L35" t="n">
         <v>2.5</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>4.7</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45670.55208333334</v>
+        <v>45671.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>2757.2</v>
+        <v>2716.35</v>
       </c>
       <c r="I36" t="n">
         <v>2723.330824890315</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.19</v>
+        <v>-3.64</v>
       </c>
       <c r="L36" t="n">
-        <v>3.39</v>
+        <v>3.83</v>
       </c>
       <c r="M36" t="n">
         <v>0.29</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>7.47</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>2768</v>
+        <v>2843</v>
       </c>
       <c r="I37" t="n">
         <v>2811.255234346081</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.9</v>
+        <v>-4.66</v>
       </c>
       <c r="L37" t="n">
-        <v>3.08</v>
+        <v>5.29</v>
       </c>
       <c r="M37" t="n">
         <v>0.63</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>7.6</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45693.55208333334</v>
+        <v>45694.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>2705.6</v>
+        <v>2668.35</v>
       </c>
       <c r="I38" t="n">
         <v>2697.821029126655</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.83</v>
+        <v>-6.14</v>
       </c>
       <c r="L38" t="n">
-        <v>5.08</v>
+        <v>6.31</v>
       </c>
       <c r="M38" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="N38" t="n">
         <v>4.78</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.61</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45755.55208333334</v>
+        <v>45756.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>2442</v>
+        <v>2508.65</v>
       </c>
       <c r="I39" t="n">
         <v>2476.741847016117</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K39" t="n">
-        <v>8.48</v>
+        <v>5.98</v>
       </c>
       <c r="L39" t="n">
         <v>1.71</v>
@@ -2664,7 +3131,7 @@
         <v>0.9</v>
       </c>
       <c r="N39" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="O39" t="n">
         <v>-1.4</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>6.68</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45777.38541666666</v>
+        <v>45777.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>2599</v>
+        <v>2577.3</v>
       </c>
       <c r="I40" t="n">
         <v>2580.902657943544</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>3.6</v>
+        <v>2.74</v>
       </c>
       <c r="L40" t="n">
         <v>2.62</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>5.76</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45792.38541666666</v>
+        <v>45792.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>2615</v>
+        <v>2660</v>
       </c>
       <c r="I41" t="n">
         <v>2659.693021960954</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.46</v>
+        <v>-3.21</v>
       </c>
       <c r="L41" t="n">
-        <v>2.7</v>
+        <v>3.21</v>
       </c>
       <c r="M41" t="n">
         <v>1.23</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>5.28</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45798.55208333334</v>
+        <v>45799.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>2660</v>
+        <v>2523.2</v>
       </c>
       <c r="I42" t="n">
         <v>2588.158317790796</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>-5.14</v>
       </c>
       <c r="L42" t="n">
-        <v>1.76</v>
+        <v>5.9</v>
       </c>
       <c r="M42" t="n">
-        <v>0.01</v>
+        <v>2.29</v>
       </c>
       <c r="N42" t="n">
-        <v>2.58</v>
+        <v>6.54</v>
       </c>
       <c r="O42" t="n">
         <v>1.72</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.32</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45840.55208333334</v>
+        <v>45841.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>2435</v>
+        <v>2451.5</v>
       </c>
       <c r="I43" t="n">
         <v>2438.062695442166</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K43" t="n">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="L43" t="n">
         <v>3.01</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>3.94</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45849.38541666666</v>
+        <v>45849.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>2390.3</v>
+        <v>2376</v>
       </c>
       <c r="I44" t="n">
         <v>2380.533803438039</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.5</v>
+        <v>-3.08</v>
       </c>
       <c r="L44" t="n">
-        <v>2.67</v>
+        <v>3.32</v>
       </c>
       <c r="M44" t="n">
         <v>0.27</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>3.77</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>2151.1</v>
+        <v>2241.5</v>
       </c>
       <c r="I45" t="n">
         <v>2232.093965258</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>34</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K45" t="n">
-        <v>9.470000000000001</v>
+        <v>5.66</v>
       </c>
       <c r="L45" t="n">
         <v>1.52</v>
       </c>
       <c r="M45" t="n">
-        <v>0.53</v>
+        <v>2.27</v>
       </c>
       <c r="N45" t="n">
-        <v>0.86</v>
+        <v>3.3</v>
       </c>
       <c r="O45" t="n">
         <v>-1.37</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>5.34</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45922.55208333334</v>
+        <v>45923.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>2345</v>
+        <v>2333.1</v>
       </c>
       <c r="I46" t="n">
         <v>2340.132956922818</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K46" t="n">
-        <v>4.62</v>
+        <v>4.09</v>
       </c>
       <c r="L46" t="n">
         <v>2.49</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>3.03</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45945.55208333334</v>
+        <v>45946.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>2228</v>
+        <v>2278.3</v>
       </c>
       <c r="I47" t="n">
         <v>2264.294503326904</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K47" t="n">
-        <v>4.5</v>
+        <v>2.35</v>
       </c>
       <c r="L47" t="n">
         <v>0.5</v>
@@ -3120,7 +3683,7 @@
         <v>0.5</v>
       </c>
       <c r="N47" t="n">
-        <v>1.39</v>
+        <v>2.73</v>
       </c>
       <c r="O47" t="n">
         <v>-0.87</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>4.57</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45953.55208333334</v>
+        <v>45954.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>2300</v>
+        <v>2217.5</v>
       </c>
       <c r="I48" t="n">
         <v>2221.103177730497</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K48" t="n">
-        <v>0.95</v>
+        <v>-2.67</v>
       </c>
       <c r="L48" t="n">
-        <v>2.5</v>
+        <v>3.44</v>
       </c>
       <c r="M48" t="n">
-        <v>0.14</v>
+        <v>2.39</v>
       </c>
       <c r="N48" t="n">
-        <v>2.03</v>
+        <v>2.6</v>
       </c>
       <c r="O48" t="n">
         <v>2.73</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.54</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46000.38541666666</v>
+        <v>46000.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>2157.2</v>
+        <v>2172</v>
       </c>
       <c r="I49" t="n">
         <v>2171.70127838612</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K49" t="n">
-        <v>2.72</v>
+        <v>2.05</v>
       </c>
       <c r="L49" t="n">
         <v>2.8</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>3.78</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46008.38541666666</v>
+        <v>46008.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>2109.6</v>
+        <v>2083</v>
       </c>
       <c r="I50" t="n">
         <v>2106.047101123467</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.87</v>
+        <v>-4.1</v>
       </c>
       <c r="L50" t="n">
-        <v>2.96</v>
+        <v>4.45</v>
       </c>
       <c r="M50" t="n">
         <v>1.44</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>4.18</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46038.55208333334</v>
+        <v>46041.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>2106.4</v>
+        <v>2119.2</v>
       </c>
       <c r="I51" t="n">
         <v>2109.416797959276</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>30</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.12</v>
+        <v>-1.74</v>
       </c>
       <c r="L51" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="M51" t="n">
         <v>0.61</v>
       </c>
       <c r="N51" t="n">
-        <v>1.86</v>
+        <v>3.39</v>
       </c>
       <c r="O51" t="n">
         <v>-3.48</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>3.73</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46051.55208333334</v>
+        <v>46052.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>2111</v>
+        <v>2073.6</v>
       </c>
       <c r="I52" t="n">
         <v>2076.846690906443</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.39</v>
+        <v>-2.15</v>
       </c>
       <c r="L52" t="n">
-        <v>1.49</v>
+        <v>4.24</v>
       </c>
       <c r="M52" t="n">
-        <v>0.73</v>
+        <v>1.33</v>
       </c>
       <c r="N52" t="n">
         <v>2.72</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>5.76</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46063.38541666666</v>
+        <v>46063.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>2158.5</v>
+        <v>2193.3</v>
       </c>
       <c r="I53" t="n">
         <v>2192.954489008694</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.09</v>
+        <v>-5.77</v>
       </c>
       <c r="L53" t="n">
-        <v>4.27</v>
+        <v>5.81</v>
       </c>
       <c r="M53" t="n">
         <v>1.04</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.3</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46085.38541666666</v>
+        <v>46085.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>2198.6</v>
+        <v>2184.9</v>
       </c>
       <c r="I54" t="n">
         <v>2196.302908947076</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>21.83333333333333</v>
+        <v>22</v>
       </c>
       <c r="K54" t="n">
-        <v>0.24</v>
+        <v>-0.38</v>
       </c>
       <c r="L54" t="n">
         <v>4.23</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>4.85</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1849</v>
+        <v>1909.5</v>
       </c>
       <c r="I55" t="n">
         <v>1907.40712468976</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>15.37</v>
+        <v>12.6</v>
       </c>
       <c r="L55" t="n">
         <v>1.61</v>
       </c>
       <c r="M55" t="n">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="N55" t="n">
-        <v>2.27</v>
+        <v>3.14</v>
       </c>
       <c r="O55" t="n">
         <v>-1.95</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.81</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46167.55208333334</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>2100</v>
+        <v>2057.3</v>
       </c>
       <c r="I56" t="n">
         <v>2088.491557504099</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K56" t="n">
-        <v>9.98</v>
+        <v>7.74</v>
       </c>
       <c r="L56" t="n">
         <v>2.09</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.02</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46189.38541666666</v>
+        <v>46189.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>2069.2</v>
+        <v>2097.8</v>
       </c>
       <c r="I57" t="n">
         <v>2086.734874787862</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.58</v>
+        <v>-1.97</v>
       </c>
       <c r="L57" t="n">
         <v>3.85</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>5.97</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46196.55208333334</v>
+        <v>46197.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1982.1</v>
+        <v>1968.1</v>
       </c>
       <c r="I58" t="n">
         <v>1972.652551240668</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.52</v>
+        <v>-6.18</v>
       </c>
       <c r="L58" t="n">
-        <v>5.84</v>
+        <v>6.67</v>
       </c>
       <c r="M58" t="n">
         <v>0.85</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>4.78</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46203.55208333334</v>
+        <v>46204.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>2000.5</v>
+        <v>2064.9</v>
       </c>
       <c r="I59" t="n">
         <v>2060.339357987702</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.65</v>
+        <v>-4.92</v>
       </c>
       <c r="L59" t="n">
-        <v>3.09</v>
+        <v>5.2</v>
       </c>
       <c r="M59" t="n">
         <v>0.31</v>
       </c>
       <c r="N59" t="n">
-        <v>1.33</v>
+        <v>3.57</v>
       </c>
       <c r="O59" t="n">
         <v>-0.91</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.93</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46237.55208333334</v>
+        <v>46238.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>2059</v>
+        <v>2028</v>
       </c>
       <c r="I60" t="n">
         <v>2053.801981172209</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.29</v>
+        <v>-1.79</v>
       </c>
       <c r="L60" t="n">
         <v>3.81</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.33</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46280.55208333334</v>
+        <v>46281.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1830</v>
+        <v>1872</v>
       </c>
       <c r="I61" t="n">
         <v>1848.227831121062</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K61" t="n">
-        <v>9.76</v>
+        <v>7.69</v>
       </c>
       <c r="L61" t="n">
         <v>2.57</v>
@@ -3918,7 +4649,7 @@
         <v>1.65</v>
       </c>
       <c r="N61" t="n">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="O61" t="n">
         <v>-1.89</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>4.57</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46294.38541666666</v>
+        <v>46294.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>1819.9</v>
+        <v>1808.8</v>
       </c>
       <c r="I62" t="n">
         <v>1817.61181097243</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.78</v>
+        <v>-3.38</v>
       </c>
       <c r="L62" t="n">
-        <v>3.25</v>
+        <v>3.81</v>
       </c>
       <c r="M62" t="n">
         <v>0.53</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>4</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46303.55208333334</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1745.5</v>
+        <v>1838</v>
       </c>
       <c r="I63" t="n">
         <v>1803.344178047239</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K63" t="n">
-        <v>3.5</v>
+        <v>-1.61</v>
       </c>
       <c r="L63" t="n">
-        <v>0.67</v>
+        <v>3.32</v>
       </c>
       <c r="M63" t="n">
         <v>0.28</v>
       </c>
       <c r="N63" t="n">
-        <v>1.95</v>
+        <v>4.73</v>
       </c>
       <c r="O63" t="n">
         <v>-1.37</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>7.69</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1739.3</v>
+        <v>1718.7</v>
       </c>
       <c r="I64" t="n">
         <v>1727.803590589937</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.37</v>
+        <v>-6.49</v>
       </c>
       <c r="L64" t="n">
-        <v>6.25</v>
+        <v>6.51</v>
       </c>
       <c r="M64" t="n">
         <v>0.53</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,14 @@
       <c r="Q65" t="n">
         <v>12</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6251,7 +7038,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.9</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="6">
@@ -6261,7 +7048,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -6271,7 +7058,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>129.2</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8">
@@ -6281,7 +7068,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="9">
@@ -6291,7 +7078,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="10">
@@ -6301,7 +7088,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58.2</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="11">
@@ -6311,7 +7098,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -6321,7 +7108,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6331,7 +7118,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>66.7</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6341,7 +7128,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.02</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="15">
@@ -6351,7 +7138,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.47</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="16">
@@ -6361,7 +7148,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.55</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="17">
@@ -6371,7 +7158,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.89</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="18">
@@ -6381,7 +7168,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="19">
@@ -6391,7 +7178,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.26</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="20">
@@ -6401,7 +7188,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.12</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="21">
@@ -6411,7 +7198,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.25</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="22">
@@ -6421,7 +7208,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -6441,7 +7228,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="25">
@@ -6451,7 +7238,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="26">
@@ -6461,7 +7248,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.36</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="27">
@@ -6471,7 +7258,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.78</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="28">
@@ -6481,7 +7268,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
